--- a/artfynd/A 38179-2024 artfynd.xlsx
+++ b/artfynd/A 38179-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,6 +1035,108 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120348691</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553557</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7016017</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
